--- a/data/HS_048/HS_048.xlsx
+++ b/data/HS_048/HS_048.xlsx
@@ -10,8 +10,12 @@
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Catch" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="SPPR" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="PPR" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="NPP" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="sppr_all" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="sppr_inner" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="sppr_PP" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Recycling" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="PPR" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="NPP" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,13 +40,22 @@
       <b val="1"/>
       <sz val="14"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -57,7 +70,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -68,6 +81,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -434,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D57"/>
+  <dimension ref="A1:D60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -512,685 +532,716 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>catch years</t>
+          <t>model workbooks</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1973-2019</t>
+          <t>none yet</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>taxa in catch</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>19</v>
+          <t>catch years</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1973-2019</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>taxa in catch</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>taxa with a trophic level</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="B11" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>model source context</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>No pilot model selected</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>year</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>catch_tonnes</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>ppr_tonnes</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>ppr_over_npp_percent</t>
         </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>1973</v>
-      </c>
-      <c r="B13" t="n">
-        <v>40</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>1974</v>
-      </c>
-      <c r="B14" t="n">
-        <v>200</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1976</v>
+        <v>1973</v>
       </c>
       <c r="B15" t="n">
-        <v>389</v>
+        <v>40</v>
       </c>
       <c r="C15" t="n">
-        <v>74122.42200000001</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0179</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1978</v>
+        <v>1974</v>
       </c>
       <c r="B16" t="n">
-        <v>6640</v>
+        <v>200</v>
       </c>
       <c r="C16" t="n">
-        <v>1265225.917</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3056</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1979</v>
+        <v>1976</v>
       </c>
       <c r="B17" t="n">
-        <v>45734.49</v>
+        <v>389</v>
       </c>
       <c r="C17" t="n">
-        <v>8714744.185000001</v>
+        <v>74122.42200000001</v>
       </c>
       <c r="D17" t="n">
-        <v>2.1048</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1980</v>
+        <v>1978</v>
       </c>
       <c r="B18" t="n">
-        <v>77396</v>
+        <v>6640</v>
       </c>
       <c r="C18" t="n">
-        <v>14747503.773</v>
+        <v>1265225.917</v>
       </c>
       <c r="D18" t="n">
-        <v>3.5618</v>
+        <v>0.034</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1981</v>
+        <v>1979</v>
       </c>
       <c r="B19" t="n">
-        <v>100133.825</v>
+        <v>45734.49</v>
       </c>
       <c r="C19" t="n">
-        <v>19038793.766</v>
+        <v>8714744.185000001</v>
       </c>
       <c r="D19" t="n">
-        <v>4.5982</v>
+        <v>0.2339</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1982</v>
+        <v>1980</v>
       </c>
       <c r="B20" t="n">
-        <v>66562.535</v>
+        <v>77396</v>
       </c>
       <c r="C20" t="n">
-        <v>12683231.741</v>
+        <v>14747503.773</v>
       </c>
       <c r="D20" t="n">
-        <v>3.0632</v>
+        <v>0.3958</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1983</v>
+        <v>1981</v>
       </c>
       <c r="B21" t="n">
-        <v>11971</v>
+        <v>100133.825</v>
       </c>
       <c r="C21" t="n">
-        <v>2140975.663</v>
+        <v>19038793.766</v>
       </c>
       <c r="D21" t="n">
-        <v>0.5171</v>
+        <v>0.5109</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1984</v>
+        <v>1982</v>
       </c>
       <c r="B22" t="n">
-        <v>23589</v>
+        <v>66562.535</v>
       </c>
       <c r="C22" t="n">
-        <v>4494791.288</v>
+        <v>12683231.741</v>
       </c>
       <c r="D22" t="n">
-        <v>1.0856</v>
+        <v>0.3404</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1985</v>
+        <v>1983</v>
       </c>
       <c r="B23" t="n">
-        <v>15955.7</v>
+        <v>11971</v>
       </c>
       <c r="C23" t="n">
-        <v>3040295.958</v>
+        <v>2140975.663</v>
       </c>
       <c r="D23" t="n">
-        <v>0.7343</v>
+        <v>0.0575</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1986</v>
+        <v>1984</v>
       </c>
       <c r="B24" t="n">
-        <v>41525.091</v>
+        <v>23589</v>
       </c>
       <c r="C24" t="n">
-        <v>7912443.023</v>
+        <v>4494791.288</v>
       </c>
       <c r="D24" t="n">
-        <v>1.911</v>
+        <v>0.1206</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1987</v>
+        <v>1985</v>
       </c>
       <c r="B25" t="n">
-        <v>67838.90700000001</v>
+        <v>15955.7</v>
       </c>
       <c r="C25" t="n">
-        <v>12925551.732</v>
+        <v>3040295.958</v>
       </c>
       <c r="D25" t="n">
-        <v>3.1217</v>
+        <v>0.08160000000000001</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1988</v>
+        <v>1986</v>
       </c>
       <c r="B26" t="n">
-        <v>80501</v>
+        <v>41525.091</v>
       </c>
       <c r="C26" t="n">
-        <v>15261406.528</v>
+        <v>7912443.023</v>
       </c>
       <c r="D26" t="n">
-        <v>3.6859</v>
+        <v>0.2123</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1989</v>
+        <v>1987</v>
       </c>
       <c r="B27" t="n">
-        <v>106553.66</v>
+        <v>67838.90700000001</v>
       </c>
       <c r="C27" t="n">
-        <v>20303381.349</v>
+        <v>12925551.732</v>
       </c>
       <c r="D27" t="n">
-        <v>4.9036</v>
+        <v>0.3469</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>1990</v>
+        <v>1988</v>
       </c>
       <c r="B28" t="n">
-        <v>42783.57</v>
+        <v>80501</v>
       </c>
       <c r="C28" t="n">
-        <v>8152241.201</v>
+        <v>15261406.528</v>
       </c>
       <c r="D28" t="n">
-        <v>1.9689</v>
+        <v>0.4095</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1991</v>
+        <v>1989</v>
       </c>
       <c r="B29" t="n">
-        <v>72168.50999999999</v>
+        <v>106553.66</v>
       </c>
       <c r="C29" t="n">
-        <v>13745709.706</v>
+        <v>20303381.349</v>
       </c>
       <c r="D29" t="n">
-        <v>3.3198</v>
+        <v>0.5448</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1992</v>
+        <v>1990</v>
       </c>
       <c r="B30" t="n">
-        <v>72930.8</v>
+        <v>42783.57</v>
       </c>
       <c r="C30" t="n">
-        <v>13896677.453</v>
+        <v>8152241.201</v>
       </c>
       <c r="D30" t="n">
-        <v>3.3563</v>
+        <v>0.2188</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1993</v>
+        <v>1991</v>
       </c>
       <c r="B31" t="n">
-        <v>33422.157</v>
+        <v>72168.50999999999</v>
       </c>
       <c r="C31" t="n">
-        <v>6338275.42</v>
+        <v>13745709.706</v>
       </c>
       <c r="D31" t="n">
-        <v>1.5308</v>
+        <v>0.3689</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>1994</v>
+        <v>1992</v>
       </c>
       <c r="B32" t="n">
-        <v>45194.261</v>
+        <v>72930.8</v>
       </c>
       <c r="C32" t="n">
-        <v>8595465.175000001</v>
+        <v>13896677.453</v>
       </c>
       <c r="D32" t="n">
-        <v>2.076</v>
+        <v>0.3729</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>1995</v>
+        <v>1993</v>
       </c>
       <c r="B33" t="n">
-        <v>42417.997</v>
+        <v>33422.157</v>
       </c>
       <c r="C33" t="n">
-        <v>8081833.878</v>
+        <v>6338275.42</v>
       </c>
       <c r="D33" t="n">
-        <v>1.9519</v>
+        <v>0.1701</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>1996</v>
+        <v>1994</v>
       </c>
       <c r="B34" t="n">
-        <v>60245.844</v>
+        <v>45194.261</v>
       </c>
       <c r="C34" t="n">
-        <v>11478883.015</v>
+        <v>8595465.175000001</v>
       </c>
       <c r="D34" t="n">
-        <v>2.7724</v>
+        <v>0.2307</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>1997</v>
+        <v>1995</v>
       </c>
       <c r="B35" t="n">
-        <v>49011.105</v>
+        <v>42417.997</v>
       </c>
       <c r="C35" t="n">
-        <v>9338456.188999999</v>
+        <v>8081833.878</v>
       </c>
       <c r="D35" t="n">
-        <v>2.2554</v>
+        <v>0.2169</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>1998</v>
+        <v>1996</v>
       </c>
       <c r="B36" t="n">
-        <v>55336.178</v>
+        <v>60245.844</v>
       </c>
       <c r="C36" t="n">
-        <v>10543887.156</v>
+        <v>11478883.015</v>
       </c>
       <c r="D36" t="n">
-        <v>2.5465</v>
+        <v>0.308</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>1999</v>
+        <v>1997</v>
       </c>
       <c r="B37" t="n">
-        <v>38037.257</v>
+        <v>49011.105</v>
       </c>
       <c r="C37" t="n">
-        <v>7247505.768</v>
+        <v>9338456.188999999</v>
       </c>
       <c r="D37" t="n">
-        <v>1.7504</v>
+        <v>0.2506</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>2000</v>
+        <v>1998</v>
       </c>
       <c r="B38" t="n">
-        <v>73095.7</v>
+        <v>55336.178</v>
       </c>
       <c r="C38" t="n">
-        <v>13928098.5</v>
+        <v>10543887.156</v>
       </c>
       <c r="D38" t="n">
-        <v>3.3639</v>
+        <v>0.2829</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>2001</v>
+        <v>1999</v>
       </c>
       <c r="B39" t="n">
-        <v>45078.792</v>
+        <v>38037.257</v>
       </c>
       <c r="C39" t="n">
-        <v>8589604.084000001</v>
+        <v>7247505.768</v>
       </c>
       <c r="D39" t="n">
-        <v>2.0745</v>
+        <v>0.1945</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>2002</v>
+        <v>2000</v>
       </c>
       <c r="B40" t="n">
-        <v>10734.9</v>
+        <v>73095.7</v>
       </c>
       <c r="C40" t="n">
-        <v>2045493.026</v>
+        <v>13928098.5</v>
       </c>
       <c r="D40" t="n">
-        <v>0.494</v>
+        <v>0.3738</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>2003</v>
+        <v>2001</v>
       </c>
       <c r="B41" t="n">
-        <v>35343.39</v>
+        <v>45078.792</v>
       </c>
       <c r="C41" t="n">
-        <v>6734544.128</v>
+        <v>8589604.084000001</v>
       </c>
       <c r="D41" t="n">
-        <v>1.6265</v>
+        <v>0.2305</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>2004</v>
+        <v>2002</v>
       </c>
       <c r="B42" t="n">
-        <v>13832.394</v>
+        <v>10734.9</v>
       </c>
       <c r="C42" t="n">
-        <v>2635708.392</v>
+        <v>2045493.026</v>
       </c>
       <c r="D42" t="n">
-        <v>0.6366000000000001</v>
+        <v>0.0549</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>2005</v>
+        <v>2003</v>
       </c>
       <c r="B43" t="n">
-        <v>7142.537</v>
+        <v>35343.39</v>
       </c>
       <c r="C43" t="n">
-        <v>1360975.258</v>
+        <v>6734544.128</v>
       </c>
       <c r="D43" t="n">
-        <v>0.3287</v>
+        <v>0.1807</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>2006</v>
+        <v>2004</v>
       </c>
       <c r="B44" t="n">
-        <v>90064.768</v>
+        <v>13832.394</v>
       </c>
       <c r="C44" t="n">
-        <v>17161490.541</v>
+        <v>2635708.392</v>
       </c>
       <c r="D44" t="n">
-        <v>4.1448</v>
+        <v>0.0707</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>2007</v>
+        <v>2005</v>
       </c>
       <c r="B45" t="n">
-        <v>18449.199</v>
+        <v>7142.537</v>
       </c>
       <c r="C45" t="n">
-        <v>3515405.13</v>
+        <v>1360975.258</v>
       </c>
       <c r="D45" t="n">
-        <v>0.849</v>
+        <v>0.0365</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>2008</v>
+        <v>2006</v>
       </c>
       <c r="B46" t="n">
-        <v>2016.461</v>
+        <v>90064.768</v>
       </c>
       <c r="C46" t="n">
-        <v>384228.687</v>
+        <v>17161490.541</v>
       </c>
       <c r="D46" t="n">
-        <v>0.09279999999999999</v>
+        <v>0.4605</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>2009</v>
+        <v>2007</v>
       </c>
       <c r="B47" t="n">
-        <v>34946.427</v>
+        <v>18449.199</v>
       </c>
       <c r="C47" t="n">
-        <v>6659024.795</v>
+        <v>3515405.13</v>
       </c>
       <c r="D47" t="n">
-        <v>1.6083</v>
+        <v>0.09429999999999999</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="B48" t="n">
-        <v>155683.373</v>
+        <v>2016.461</v>
       </c>
       <c r="C48" t="n">
-        <v>29664854.738</v>
+        <v>384228.687</v>
       </c>
       <c r="D48" t="n">
-        <v>7.1646</v>
+        <v>0.0103</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>2011</v>
+        <v>2009</v>
       </c>
       <c r="B49" t="n">
-        <v>18187.038</v>
+        <v>34946.427</v>
       </c>
       <c r="C49" t="n">
-        <v>3465468.605</v>
+        <v>6659024.795</v>
       </c>
       <c r="D49" t="n">
-        <v>0.837</v>
+        <v>0.1787</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="B50" t="n">
-        <v>64757.852</v>
+        <v>155683.373</v>
       </c>
       <c r="C50" t="n">
-        <v>12339354.51</v>
+        <v>29664854.738</v>
       </c>
       <c r="D50" t="n">
-        <v>2.9802</v>
+        <v>0.7961</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>2013</v>
+        <v>2011</v>
       </c>
       <c r="B51" t="n">
-        <v>166266.6</v>
+        <v>18187.038</v>
       </c>
       <c r="C51" t="n">
-        <v>31669675.505</v>
+        <v>3465468.605</v>
       </c>
       <c r="D51" t="n">
-        <v>7.6488</v>
+        <v>0.093</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="B52" t="n">
-        <v>135353.698</v>
+        <v>64757.852</v>
       </c>
       <c r="C52" t="n">
-        <v>25747181.179</v>
+        <v>12339354.51</v>
       </c>
       <c r="D52" t="n">
-        <v>6.2184</v>
+        <v>0.3311</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>2015</v>
+        <v>2013</v>
       </c>
       <c r="B53" t="n">
-        <v>164589.025</v>
+        <v>166266.6</v>
       </c>
       <c r="C53" t="n">
-        <v>31361792.173</v>
+        <v>31669675.505</v>
       </c>
       <c r="D53" t="n">
-        <v>7.5744</v>
+        <v>0.8499</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="B54" t="n">
-        <v>143201.742</v>
+        <v>135353.698</v>
       </c>
       <c r="C54" t="n">
-        <v>27286529.878</v>
+        <v>25747181.179</v>
       </c>
       <c r="D54" t="n">
-        <v>6.5902</v>
+        <v>0.6909</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>2017</v>
+        <v>2015</v>
       </c>
       <c r="B55" t="n">
-        <v>149682.934</v>
+        <v>164589.025</v>
       </c>
       <c r="C55" t="n">
-        <v>28520779.835</v>
+        <v>31361792.173</v>
       </c>
       <c r="D55" t="n">
-        <v>6.8883</v>
+        <v>0.8416</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="B56" t="n">
-        <v>153112.197</v>
+        <v>143201.742</v>
       </c>
       <c r="C56" t="n">
-        <v>29174931.261</v>
+        <v>27286529.878</v>
       </c>
       <c r="D56" t="n">
-        <v>7.0463</v>
+        <v>0.7322</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B57" t="n">
+        <v>149682.934</v>
+      </c>
+      <c r="C57" t="n">
+        <v>28520779.835</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0.7654</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B58" t="n">
+        <v>153112.197</v>
+      </c>
+      <c r="C58" t="n">
+        <v>29174931.261</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0.7829</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
         <v>2019</v>
       </c>
-      <c r="B57" t="n">
+      <c r="B59" t="n">
         <v>154127.615</v>
       </c>
-      <c r="C57" t="n">
+      <c r="C59" t="n">
         <v>29368420.191</v>
       </c>
-      <c r="D57" t="n">
-        <v>7.093</v>
+      <c r="D59" t="n">
+        <v>0.7881</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>PPR/NPP converts wet-weight PP to carbon at 9:1; NPP is the fixed 2019 ensemble median.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1279,230 +1330,140 @@
           <t>commercial_group</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>1973</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>1974</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>1976</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>1978</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>1979</t>
-        </is>
-      </c>
-      <c r="J1" s="2" t="inlineStr">
-        <is>
-          <t>1980</t>
-        </is>
-      </c>
-      <c r="K1" s="2" t="inlineStr">
-        <is>
-          <t>1981</t>
-        </is>
-      </c>
-      <c r="L1" s="2" t="inlineStr">
-        <is>
-          <t>1982</t>
-        </is>
-      </c>
-      <c r="M1" s="2" t="inlineStr">
-        <is>
-          <t>1983</t>
-        </is>
-      </c>
-      <c r="N1" s="2" t="inlineStr">
-        <is>
-          <t>1984</t>
-        </is>
-      </c>
-      <c r="O1" s="2" t="inlineStr">
-        <is>
-          <t>1985</t>
-        </is>
-      </c>
-      <c r="P1" s="2" t="inlineStr">
-        <is>
-          <t>1986</t>
-        </is>
-      </c>
-      <c r="Q1" s="2" t="inlineStr">
-        <is>
-          <t>1987</t>
-        </is>
-      </c>
-      <c r="R1" s="2" t="inlineStr">
-        <is>
-          <t>1988</t>
-        </is>
-      </c>
-      <c r="S1" s="2" t="inlineStr">
-        <is>
-          <t>1989</t>
-        </is>
-      </c>
-      <c r="T1" s="2" t="inlineStr">
-        <is>
-          <t>1990</t>
-        </is>
-      </c>
-      <c r="U1" s="2" t="inlineStr">
-        <is>
-          <t>1991</t>
-        </is>
-      </c>
-      <c r="V1" s="2" t="inlineStr">
-        <is>
-          <t>1992</t>
-        </is>
-      </c>
-      <c r="W1" s="2" t="inlineStr">
-        <is>
-          <t>1993</t>
-        </is>
-      </c>
-      <c r="X1" s="2" t="inlineStr">
-        <is>
-          <t>1994</t>
-        </is>
-      </c>
-      <c r="Y1" s="2" t="inlineStr">
-        <is>
-          <t>1995</t>
-        </is>
-      </c>
-      <c r="Z1" s="2" t="inlineStr">
-        <is>
-          <t>1996</t>
-        </is>
-      </c>
-      <c r="AA1" s="2" t="inlineStr">
-        <is>
-          <t>1997</t>
-        </is>
-      </c>
-      <c r="AB1" s="2" t="inlineStr">
-        <is>
-          <t>1998</t>
-        </is>
-      </c>
-      <c r="AC1" s="2" t="inlineStr">
-        <is>
-          <t>1999</t>
-        </is>
-      </c>
-      <c r="AD1" s="2" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="AE1" s="2" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="AF1" s="2" t="inlineStr">
-        <is>
-          <t>2002</t>
-        </is>
-      </c>
-      <c r="AG1" s="2" t="inlineStr">
-        <is>
-          <t>2003</t>
-        </is>
-      </c>
-      <c r="AH1" s="2" t="inlineStr">
-        <is>
-          <t>2004</t>
-        </is>
-      </c>
-      <c r="AI1" s="2" t="inlineStr">
-        <is>
-          <t>2005</t>
-        </is>
-      </c>
-      <c r="AJ1" s="2" t="inlineStr">
-        <is>
-          <t>2006</t>
-        </is>
-      </c>
-      <c r="AK1" s="2" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="AL1" s="2" t="inlineStr">
-        <is>
-          <t>2008</t>
-        </is>
-      </c>
-      <c r="AM1" s="2" t="inlineStr">
-        <is>
-          <t>2009</t>
-        </is>
-      </c>
-      <c r="AN1" s="2" t="inlineStr">
-        <is>
-          <t>2010</t>
-        </is>
-      </c>
-      <c r="AO1" s="2" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
-      </c>
-      <c r="AP1" s="2" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="AQ1" s="2" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-      <c r="AR1" s="2" t="inlineStr">
-        <is>
-          <t>2014</t>
-        </is>
-      </c>
-      <c r="AS1" s="2" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-      <c r="AT1" s="2" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="AU1" s="2" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="AV1" s="2" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="AW1" s="2" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
+      <c r="E1" s="2" t="n">
+        <v>1973</v>
+      </c>
+      <c r="F1" s="2" t="n">
+        <v>1974</v>
+      </c>
+      <c r="G1" s="2" t="n">
+        <v>1976</v>
+      </c>
+      <c r="H1" s="2" t="n">
+        <v>1978</v>
+      </c>
+      <c r="I1" s="2" t="n">
+        <v>1979</v>
+      </c>
+      <c r="J1" s="2" t="n">
+        <v>1980</v>
+      </c>
+      <c r="K1" s="2" t="n">
+        <v>1981</v>
+      </c>
+      <c r="L1" s="2" t="n">
+        <v>1982</v>
+      </c>
+      <c r="M1" s="2" t="n">
+        <v>1983</v>
+      </c>
+      <c r="N1" s="2" t="n">
+        <v>1984</v>
+      </c>
+      <c r="O1" s="2" t="n">
+        <v>1985</v>
+      </c>
+      <c r="P1" s="2" t="n">
+        <v>1986</v>
+      </c>
+      <c r="Q1" s="2" t="n">
+        <v>1987</v>
+      </c>
+      <c r="R1" s="2" t="n">
+        <v>1988</v>
+      </c>
+      <c r="S1" s="2" t="n">
+        <v>1989</v>
+      </c>
+      <c r="T1" s="2" t="n">
+        <v>1990</v>
+      </c>
+      <c r="U1" s="2" t="n">
+        <v>1991</v>
+      </c>
+      <c r="V1" s="2" t="n">
+        <v>1992</v>
+      </c>
+      <c r="W1" s="2" t="n">
+        <v>1993</v>
+      </c>
+      <c r="X1" s="2" t="n">
+        <v>1994</v>
+      </c>
+      <c r="Y1" s="2" t="n">
+        <v>1995</v>
+      </c>
+      <c r="Z1" s="2" t="n">
+        <v>1996</v>
+      </c>
+      <c r="AA1" s="2" t="n">
+        <v>1997</v>
+      </c>
+      <c r="AB1" s="2" t="n">
+        <v>1998</v>
+      </c>
+      <c r="AC1" s="2" t="n">
+        <v>1999</v>
+      </c>
+      <c r="AD1" s="2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="AE1" s="2" t="n">
+        <v>2001</v>
+      </c>
+      <c r="AF1" s="2" t="n">
+        <v>2002</v>
+      </c>
+      <c r="AG1" s="2" t="n">
+        <v>2003</v>
+      </c>
+      <c r="AH1" s="2" t="n">
+        <v>2004</v>
+      </c>
+      <c r="AI1" s="2" t="n">
+        <v>2005</v>
+      </c>
+      <c r="AJ1" s="2" t="n">
+        <v>2006</v>
+      </c>
+      <c r="AK1" s="2" t="n">
+        <v>2007</v>
+      </c>
+      <c r="AL1" s="2" t="n">
+        <v>2008</v>
+      </c>
+      <c r="AM1" s="2" t="n">
+        <v>2009</v>
+      </c>
+      <c r="AN1" s="2" t="n">
+        <v>2010</v>
+      </c>
+      <c r="AO1" s="2" t="n">
+        <v>2011</v>
+      </c>
+      <c r="AP1" s="2" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AQ1" s="2" t="n">
+        <v>2013</v>
+      </c>
+      <c r="AR1" s="2" t="n">
+        <v>2014</v>
+      </c>
+      <c r="AS1" s="2" t="n">
+        <v>2015</v>
+      </c>
+      <c r="AT1" s="2" t="n">
+        <v>2016</v>
+      </c>
+      <c r="AU1" s="2" t="n">
+        <v>2017</v>
+      </c>
+      <c r="AV1" s="2" t="n">
+        <v>2018</v>
+      </c>
+      <c r="AW1" s="2" t="n">
+        <v>2019</v>
       </c>
     </row>
     <row r="2">
@@ -4638,6 +4599,245 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Group SPPR: all</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>All basal sources, including imports. Models are separate. Blank means unavailable, not zero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>group_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>No extracted model is available for this ecosystem.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Group SPPR: inner</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Internal sources: primary producers and detritus; excludes imports. Models are separate. Blank means unavailable, not zero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>group_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>No extracted model is available for this ecosystem.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Group SPPR: PP</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Primary producers only; excludes detritus and imports. Models are separate. Blank means unavailable, not zero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>group_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>No extracted model is available for this ecosystem.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="90" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Recycling diagnostics from diagnose_sppr()</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>b: detrital recycling; rho living: living food-web cycles. Each must be below 1 for convergence; these are necessary, not sufficient checks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>TE_option</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>rho living</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>diagnostic status</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>b converges</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>living converges</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>input balanced</t>
+        </is>
+      </c>
+      <c r="I4" s="7" t="inlineStr">
+        <is>
+          <t>configuration</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4766,230 +4966,140 @@
           <t>trophic_level</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>1973</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>1974</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>1976</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>1978</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>1979</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>1980</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>1981</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>1982</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>1983</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>1984</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>1985</t>
-        </is>
-      </c>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
-          <t>1986</t>
-        </is>
-      </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>1987</t>
-        </is>
-      </c>
-      <c r="P4" s="3" t="inlineStr">
-        <is>
-          <t>1988</t>
-        </is>
-      </c>
-      <c r="Q4" s="3" t="inlineStr">
-        <is>
-          <t>1989</t>
-        </is>
-      </c>
-      <c r="R4" s="3" t="inlineStr">
-        <is>
-          <t>1990</t>
-        </is>
-      </c>
-      <c r="S4" s="3" t="inlineStr">
-        <is>
-          <t>1991</t>
-        </is>
-      </c>
-      <c r="T4" s="3" t="inlineStr">
-        <is>
-          <t>1992</t>
-        </is>
-      </c>
-      <c r="U4" s="3" t="inlineStr">
-        <is>
-          <t>1993</t>
-        </is>
-      </c>
-      <c r="V4" s="3" t="inlineStr">
-        <is>
-          <t>1994</t>
-        </is>
-      </c>
-      <c r="W4" s="3" t="inlineStr">
-        <is>
-          <t>1995</t>
-        </is>
-      </c>
-      <c r="X4" s="3" t="inlineStr">
-        <is>
-          <t>1996</t>
-        </is>
-      </c>
-      <c r="Y4" s="3" t="inlineStr">
-        <is>
-          <t>1997</t>
-        </is>
-      </c>
-      <c r="Z4" s="3" t="inlineStr">
-        <is>
-          <t>1998</t>
-        </is>
-      </c>
-      <c r="AA4" s="3" t="inlineStr">
-        <is>
-          <t>1999</t>
-        </is>
-      </c>
-      <c r="AB4" s="3" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="AC4" s="3" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="AD4" s="3" t="inlineStr">
-        <is>
-          <t>2002</t>
-        </is>
-      </c>
-      <c r="AE4" s="3" t="inlineStr">
-        <is>
-          <t>2003</t>
-        </is>
-      </c>
-      <c r="AF4" s="3" t="inlineStr">
-        <is>
-          <t>2004</t>
-        </is>
-      </c>
-      <c r="AG4" s="3" t="inlineStr">
-        <is>
-          <t>2005</t>
-        </is>
-      </c>
-      <c r="AH4" s="3" t="inlineStr">
-        <is>
-          <t>2006</t>
-        </is>
-      </c>
-      <c r="AI4" s="3" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="AJ4" s="3" t="inlineStr">
-        <is>
-          <t>2008</t>
-        </is>
-      </c>
-      <c r="AK4" s="3" t="inlineStr">
-        <is>
-          <t>2009</t>
-        </is>
-      </c>
-      <c r="AL4" s="3" t="inlineStr">
-        <is>
-          <t>2010</t>
-        </is>
-      </c>
-      <c r="AM4" s="3" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
-      </c>
-      <c r="AN4" s="3" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="AO4" s="3" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-      <c r="AP4" s="3" t="inlineStr">
-        <is>
-          <t>2014</t>
-        </is>
-      </c>
-      <c r="AQ4" s="3" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-      <c r="AR4" s="3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="AS4" s="3" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="AT4" s="3" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="AU4" s="3" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
+      <c r="C4" s="3" t="n">
+        <v>1973</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>1974</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>1976</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>1978</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>1979</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>1980</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>1981</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>1982</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>1983</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>1984</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>1985</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>1986</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>1987</v>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>1988</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>1989</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>1990</v>
+      </c>
+      <c r="S4" s="3" t="n">
+        <v>1991</v>
+      </c>
+      <c r="T4" s="3" t="n">
+        <v>1992</v>
+      </c>
+      <c r="U4" s="3" t="n">
+        <v>1993</v>
+      </c>
+      <c r="V4" s="3" t="n">
+        <v>1994</v>
+      </c>
+      <c r="W4" s="3" t="n">
+        <v>1995</v>
+      </c>
+      <c r="X4" s="3" t="n">
+        <v>1996</v>
+      </c>
+      <c r="Y4" s="3" t="n">
+        <v>1997</v>
+      </c>
+      <c r="Z4" s="3" t="n">
+        <v>1998</v>
+      </c>
+      <c r="AA4" s="3" t="n">
+        <v>1999</v>
+      </c>
+      <c r="AB4" s="3" t="n">
+        <v>2000</v>
+      </c>
+      <c r="AC4" s="3" t="n">
+        <v>2001</v>
+      </c>
+      <c r="AD4" s="3" t="n">
+        <v>2002</v>
+      </c>
+      <c r="AE4" s="3" t="n">
+        <v>2003</v>
+      </c>
+      <c r="AF4" s="3" t="n">
+        <v>2004</v>
+      </c>
+      <c r="AG4" s="3" t="n">
+        <v>2005</v>
+      </c>
+      <c r="AH4" s="3" t="n">
+        <v>2006</v>
+      </c>
+      <c r="AI4" s="3" t="n">
+        <v>2007</v>
+      </c>
+      <c r="AJ4" s="3" t="n">
+        <v>2008</v>
+      </c>
+      <c r="AK4" s="3" t="n">
+        <v>2009</v>
+      </c>
+      <c r="AL4" s="3" t="n">
+        <v>2010</v>
+      </c>
+      <c r="AM4" s="3" t="n">
+        <v>2011</v>
+      </c>
+      <c r="AN4" s="3" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AO4" s="3" t="n">
+        <v>2013</v>
+      </c>
+      <c r="AP4" s="3" t="n">
+        <v>2014</v>
+      </c>
+      <c r="AQ4" s="3" t="n">
+        <v>2015</v>
+      </c>
+      <c r="AR4" s="3" t="n">
+        <v>2016</v>
+      </c>
+      <c r="AS4" s="3" t="n">
+        <v>2017</v>
+      </c>
+      <c r="AT4" s="3" t="n">
+        <v>2018</v>
+      </c>
+      <c r="AU4" s="3" t="n">
+        <v>2019</v>
       </c>
     </row>
     <row r="5">
@@ -5867,7 +5977,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/data/HS_048/HS_048.xlsx
+++ b/data/HS_048/HS_048.xlsx
@@ -9,15 +9,18 @@
   <sheets>
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Catch" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="SPPR" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="sppr_all" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="sppr_inner" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="sppr_PP" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Recycling" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="PPR" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="NPP" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Final mappings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="SPPR" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="sppr_all" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="sppr_inner" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="sppr_PP" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Recycling" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="PPR" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="NPP" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'NPP'!$A$3:$O$48</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -454,13 +457,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D60"/>
+  <dimension ref="A1:D61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -617,9 +620,6 @@
       <c r="C15" t="n">
         <v>0</v>
       </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -631,9 +631,6 @@
       <c r="C16" t="n">
         <v>0</v>
       </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -645,9 +642,6 @@
       <c r="C17" t="n">
         <v>74122.42200000001</v>
       </c>
-      <c r="D17" t="n">
-        <v>0.002</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -659,9 +653,6 @@
       <c r="C18" t="n">
         <v>1265225.917</v>
       </c>
-      <c r="D18" t="n">
-        <v>0.034</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -673,9 +664,6 @@
       <c r="C19" t="n">
         <v>8714744.185000001</v>
       </c>
-      <c r="D19" t="n">
-        <v>0.2339</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -687,9 +675,6 @@
       <c r="C20" t="n">
         <v>14747503.773</v>
       </c>
-      <c r="D20" t="n">
-        <v>0.3958</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -701,9 +686,6 @@
       <c r="C21" t="n">
         <v>19038793.766</v>
       </c>
-      <c r="D21" t="n">
-        <v>0.5109</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -715,9 +697,6 @@
       <c r="C22" t="n">
         <v>12683231.741</v>
       </c>
-      <c r="D22" t="n">
-        <v>0.3404</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -729,9 +708,6 @@
       <c r="C23" t="n">
         <v>2140975.663</v>
       </c>
-      <c r="D23" t="n">
-        <v>0.0575</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -743,9 +719,6 @@
       <c r="C24" t="n">
         <v>4494791.288</v>
       </c>
-      <c r="D24" t="n">
-        <v>0.1206</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -757,9 +730,6 @@
       <c r="C25" t="n">
         <v>3040295.958</v>
       </c>
-      <c r="D25" t="n">
-        <v>0.08160000000000001</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -771,9 +741,6 @@
       <c r="C26" t="n">
         <v>7912443.023</v>
       </c>
-      <c r="D26" t="n">
-        <v>0.2123</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -785,9 +752,6 @@
       <c r="C27" t="n">
         <v>12925551.732</v>
       </c>
-      <c r="D27" t="n">
-        <v>0.3469</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -799,9 +763,6 @@
       <c r="C28" t="n">
         <v>15261406.528</v>
       </c>
-      <c r="D28" t="n">
-        <v>0.4095</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -813,9 +774,6 @@
       <c r="C29" t="n">
         <v>20303381.349</v>
       </c>
-      <c r="D29" t="n">
-        <v>0.5448</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -827,9 +785,6 @@
       <c r="C30" t="n">
         <v>8152241.201</v>
       </c>
-      <c r="D30" t="n">
-        <v>0.2188</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -841,9 +796,6 @@
       <c r="C31" t="n">
         <v>13745709.706</v>
       </c>
-      <c r="D31" t="n">
-        <v>0.3689</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -855,9 +807,6 @@
       <c r="C32" t="n">
         <v>13896677.453</v>
       </c>
-      <c r="D32" t="n">
-        <v>0.3729</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -869,9 +818,6 @@
       <c r="C33" t="n">
         <v>6338275.42</v>
       </c>
-      <c r="D33" t="n">
-        <v>0.1701</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -883,9 +829,6 @@
       <c r="C34" t="n">
         <v>8595465.175000001</v>
       </c>
-      <c r="D34" t="n">
-        <v>0.2307</v>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -897,9 +840,6 @@
       <c r="C35" t="n">
         <v>8081833.878</v>
       </c>
-      <c r="D35" t="n">
-        <v>0.2169</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -911,9 +851,6 @@
       <c r="C36" t="n">
         <v>11478883.015</v>
       </c>
-      <c r="D36" t="n">
-        <v>0.308</v>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -925,9 +862,6 @@
       <c r="C37" t="n">
         <v>9338456.188999999</v>
       </c>
-      <c r="D37" t="n">
-        <v>0.2506</v>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -940,7 +874,7 @@
         <v>10543887.156</v>
       </c>
       <c r="D38" t="n">
-        <v>0.2829</v>
+        <v>0.2282</v>
       </c>
     </row>
     <row r="39">
@@ -954,7 +888,7 @@
         <v>7247505.768</v>
       </c>
       <c r="D39" t="n">
-        <v>0.1945</v>
+        <v>0.1469</v>
       </c>
     </row>
     <row r="40">
@@ -968,7 +902,7 @@
         <v>13928098.5</v>
       </c>
       <c r="D40" t="n">
-        <v>0.3738</v>
+        <v>0.2694</v>
       </c>
     </row>
     <row r="41">
@@ -982,7 +916,7 @@
         <v>8589604.084000001</v>
       </c>
       <c r="D41" t="n">
-        <v>0.2305</v>
+        <v>0.1874</v>
       </c>
     </row>
     <row r="42">
@@ -996,7 +930,7 @@
         <v>2045493.026</v>
       </c>
       <c r="D42" t="n">
-        <v>0.0549</v>
+        <v>0.0463</v>
       </c>
     </row>
     <row r="43">
@@ -1010,7 +944,7 @@
         <v>6734544.128</v>
       </c>
       <c r="D43" t="n">
-        <v>0.1807</v>
+        <v>0.142</v>
       </c>
     </row>
     <row r="44">
@@ -1024,7 +958,7 @@
         <v>2635708.392</v>
       </c>
       <c r="D44" t="n">
-        <v>0.0707</v>
+        <v>0.0594</v>
       </c>
     </row>
     <row r="45">
@@ -1038,7 +972,7 @@
         <v>1360975.258</v>
       </c>
       <c r="D45" t="n">
-        <v>0.0365</v>
+        <v>0.0297</v>
       </c>
     </row>
     <row r="46">
@@ -1052,7 +986,7 @@
         <v>17161490.541</v>
       </c>
       <c r="D46" t="n">
-        <v>0.4605</v>
+        <v>0.3869</v>
       </c>
     </row>
     <row r="47">
@@ -1066,7 +1000,7 @@
         <v>3515405.13</v>
       </c>
       <c r="D47" t="n">
-        <v>0.09429999999999999</v>
+        <v>0.0905</v>
       </c>
     </row>
     <row r="48">
@@ -1080,7 +1014,7 @@
         <v>384228.687</v>
       </c>
       <c r="D48" t="n">
-        <v>0.0103</v>
+        <v>0.0098</v>
       </c>
     </row>
     <row r="49">
@@ -1094,7 +1028,7 @@
         <v>6659024.795</v>
       </c>
       <c r="D49" t="n">
-        <v>0.1787</v>
+        <v>0.1388</v>
       </c>
     </row>
     <row r="50">
@@ -1108,7 +1042,7 @@
         <v>29664854.738</v>
       </c>
       <c r="D50" t="n">
-        <v>0.7961</v>
+        <v>0.5886</v>
       </c>
     </row>
     <row r="51">
@@ -1122,7 +1056,7 @@
         <v>3465468.605</v>
       </c>
       <c r="D51" t="n">
-        <v>0.093</v>
+        <v>0.07199999999999999</v>
       </c>
     </row>
     <row r="52">
@@ -1136,7 +1070,7 @@
         <v>12339354.51</v>
       </c>
       <c r="D52" t="n">
-        <v>0.3311</v>
+        <v>0.2626</v>
       </c>
     </row>
     <row r="53">
@@ -1150,7 +1084,7 @@
         <v>31669675.505</v>
       </c>
       <c r="D53" t="n">
-        <v>0.8499</v>
+        <v>0.7297</v>
       </c>
     </row>
     <row r="54">
@@ -1164,7 +1098,7 @@
         <v>25747181.179</v>
       </c>
       <c r="D54" t="n">
-        <v>0.6909</v>
+        <v>0.6199</v>
       </c>
     </row>
     <row r="55">
@@ -1178,7 +1112,7 @@
         <v>31361792.173</v>
       </c>
       <c r="D55" t="n">
-        <v>0.8416</v>
+        <v>0.7604</v>
       </c>
     </row>
     <row r="56">
@@ -1192,7 +1126,7 @@
         <v>27286529.878</v>
       </c>
       <c r="D56" t="n">
-        <v>0.7322</v>
+        <v>0.6356000000000001</v>
       </c>
     </row>
     <row r="57">
@@ -1206,7 +1140,7 @@
         <v>28520779.835</v>
       </c>
       <c r="D57" t="n">
-        <v>0.7654</v>
+        <v>0.7229</v>
       </c>
     </row>
     <row r="58">
@@ -1220,7 +1154,7 @@
         <v>29174931.261</v>
       </c>
       <c r="D58" t="n">
-        <v>0.7829</v>
+        <v>0.7631</v>
       </c>
     </row>
     <row r="59">
@@ -1234,17 +1168,1756 @@
         <v>29368420.191</v>
       </c>
       <c r="D59" t="n">
-        <v>0.7881</v>
+        <v>0.6696</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>PPR/NPP converts wet-weight PP to carbon at 9:1; NPP is the fixed 2019 ensemble median.</t>
+          <t>PPR/NPP converts wet-weight PP to carbon at 9:1 and uses the matching year's NPP ensemble median.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>PPR/NPP is blank for years without NPP; see NPP for availability and provenance.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O48"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="23" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="60" customWidth="1" min="11" max="11"/>
+    <col width="75" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="36" customWidth="1" min="14" max="14"/>
+    <col width="65" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Annual net primary production, tonnes carbon per year</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>PPR/NPP uses the ensemble median for the matching catch year. Blank values are unavailable; no year is substituted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>npp_antoinemorel_tC_yr</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>npp_vgpm_tC_yr</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>npp_eppley_tC_yr</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>npp_cbpm_tC_yr</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>npp_cafe_tC_yr</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>ens_median_tC_yr</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>ens_min_tC_yr</t>
+        </is>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>ens_max_tC_yr</t>
+        </is>
+      </c>
+      <c r="J3" s="7" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="K3" s="7" t="inlineStr">
+        <is>
+          <t>reason</t>
+        </is>
+      </c>
+      <c r="L3" s="7" t="inlineStr">
+        <is>
+          <t>provenance</t>
+        </is>
+      </c>
+      <c r="M3" s="7" t="inlineStr">
+        <is>
+          <t>n_models</t>
+        </is>
+      </c>
+      <c r="N3" s="7" t="inlineStr">
+        <is>
+          <t>available_models</t>
+        </is>
+      </c>
+      <c r="O3" s="7" t="inlineStr">
+        <is>
+          <t>ensemble_basis</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1973</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1974</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1976</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1978</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1979</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1980</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1981</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1982</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1983</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1984</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1985</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1986</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1987</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>1988</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>1990</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>1991</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>1992</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1993</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1994</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>1995</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>1996</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>1997</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>1998</v>
+      </c>
+      <c r="B27" t="n">
+        <v>513342729.7761512</v>
+      </c>
+      <c r="G27" t="n">
+        <v>513342729.7761512</v>
+      </c>
+      <c r="H27" t="n">
+        <v>513342729.7761512</v>
+      </c>
+      <c r="I27" t="n">
+        <v>513342729.7761512</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>vgpm: unsupported_year; eppley: unsupported_year; cbpm: unsupported_year; cafe: unsupported_year</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/1998/65dfd93f461846d2/provenance.json</t>
+        </is>
+      </c>
+      <c r="M27" t="n">
+        <v>1</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>antoinemorel</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>1999</v>
+      </c>
+      <c r="B28" t="n">
+        <v>548058061.016696</v>
+      </c>
+      <c r="G28" t="n">
+        <v>548058061.016696</v>
+      </c>
+      <c r="H28" t="n">
+        <v>548058061.016696</v>
+      </c>
+      <c r="I28" t="n">
+        <v>548058061.016696</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>vgpm: unsupported_year; eppley: unsupported_year; cbpm: unsupported_year; cafe: unsupported_year</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/1999/4b1cb2d6cba203fb/provenance.json</t>
+        </is>
+      </c>
+      <c r="M28" t="n">
+        <v>1</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>antoinemorel</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>2000</v>
+      </c>
+      <c r="B29" t="n">
+        <v>574348244.5365204</v>
+      </c>
+      <c r="G29" t="n">
+        <v>574348244.5365204</v>
+      </c>
+      <c r="H29" t="n">
+        <v>574348244.5365204</v>
+      </c>
+      <c r="I29" t="n">
+        <v>574348244.5365204</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>vgpm: unsupported_year; eppley: unsupported_year; cbpm: unsupported_year; cafe: unsupported_year</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2000/4bea86f4cd09bd55/provenance.json</t>
+        </is>
+      </c>
+      <c r="M29" t="n">
+        <v>1</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>antoinemorel</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>2001</v>
+      </c>
+      <c r="B30" t="n">
+        <v>509415749.1727463</v>
+      </c>
+      <c r="G30" t="n">
+        <v>509415749.1727463</v>
+      </c>
+      <c r="H30" t="n">
+        <v>509415749.1727463</v>
+      </c>
+      <c r="I30" t="n">
+        <v>509415749.1727463</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>vgpm: unsupported_year; eppley: unsupported_year; cbpm: unsupported_year; cafe: unsupported_year</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2001/0ec8617947fb90b9/provenance.json</t>
+        </is>
+      </c>
+      <c r="M30" t="n">
+        <v>1</v>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>antoinemorel</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>2002</v>
+      </c>
+      <c r="B31" t="n">
+        <v>490420635.6178724</v>
+      </c>
+      <c r="G31" t="n">
+        <v>490420635.6178724</v>
+      </c>
+      <c r="H31" t="n">
+        <v>490420635.6178724</v>
+      </c>
+      <c r="I31" t="n">
+        <v>490420635.6178724</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>vgpm: unsupported_year; eppley: unsupported_year; cbpm: unsupported_year; cafe: unsupported_year</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2002/3789d747c9365882/provenance.json</t>
+        </is>
+      </c>
+      <c r="M31" t="n">
+        <v>1</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>antoinemorel</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>2003</v>
+      </c>
+      <c r="B32" t="n">
+        <v>526913379.3396494</v>
+      </c>
+      <c r="C32" t="n">
+        <v>360268663.0603208</v>
+      </c>
+      <c r="D32" t="n">
+        <v>313484057.0591136</v>
+      </c>
+      <c r="E32" t="n">
+        <v>652980357.055828</v>
+      </c>
+      <c r="F32" t="n">
+        <v>845142418.9921153</v>
+      </c>
+      <c r="G32" t="n">
+        <v>526913379.3396494</v>
+      </c>
+      <c r="H32" t="n">
+        <v>313484057.0591136</v>
+      </c>
+      <c r="I32" t="n">
+        <v>845142418.9921153</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2003/c3a820791e3378ef/provenance.json</t>
+        </is>
+      </c>
+      <c r="M32" t="n">
+        <v>5</v>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B33" t="n">
+        <v>492848057.5885515</v>
+      </c>
+      <c r="C33" t="n">
+        <v>331896150.0530698</v>
+      </c>
+      <c r="D33" t="n">
+        <v>295091459.8375016</v>
+      </c>
+      <c r="E33" t="n">
+        <v>572545353.2911345</v>
+      </c>
+      <c r="F33" t="n">
+        <v>783268986.3053006</v>
+      </c>
+      <c r="G33" t="n">
+        <v>492848057.5885515</v>
+      </c>
+      <c r="H33" t="n">
+        <v>295091459.8375016</v>
+      </c>
+      <c r="I33" t="n">
+        <v>783268986.3053006</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2004/f4cd3b4c7fc3dd8b/provenance.json</t>
+        </is>
+      </c>
+      <c r="M33" t="n">
+        <v>5</v>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B34" t="n">
+        <v>509641871.5401881</v>
+      </c>
+      <c r="C34" t="n">
+        <v>347545624.8913146</v>
+      </c>
+      <c r="D34" t="n">
+        <v>308303684.5829442</v>
+      </c>
+      <c r="E34" t="n">
+        <v>582878475.1049339</v>
+      </c>
+      <c r="F34" t="n">
+        <v>769117369.9432724</v>
+      </c>
+      <c r="G34" t="n">
+        <v>509641871.5401881</v>
+      </c>
+      <c r="H34" t="n">
+        <v>308303684.5829442</v>
+      </c>
+      <c r="I34" t="n">
+        <v>769117369.9432724</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2005/4bdcca026379c2bd/provenance.json</t>
+        </is>
+      </c>
+      <c r="M34" t="n">
+        <v>5</v>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>2006</v>
+      </c>
+      <c r="B35" t="n">
+        <v>492794675.7049572</v>
+      </c>
+      <c r="C35" t="n">
+        <v>345632492.8650864</v>
+      </c>
+      <c r="D35" t="n">
+        <v>301848677.7338248</v>
+      </c>
+      <c r="E35" t="n">
+        <v>574605043.5057368</v>
+      </c>
+      <c r="F35" t="n">
+        <v>721532907.1412505</v>
+      </c>
+      <c r="G35" t="n">
+        <v>492794675.7049572</v>
+      </c>
+      <c r="H35" t="n">
+        <v>301848677.7338248</v>
+      </c>
+      <c r="I35" t="n">
+        <v>721532907.1412505</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2006/3ea13e28f3d7c994/provenance.json</t>
+        </is>
+      </c>
+      <c r="M35" t="n">
+        <v>5</v>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>2007</v>
+      </c>
+      <c r="B36" t="n">
+        <v>431744544.6389621</v>
+      </c>
+      <c r="C36" t="n">
+        <v>293452957.3105918</v>
+      </c>
+      <c r="D36" t="n">
+        <v>246964439.8150785</v>
+      </c>
+      <c r="E36" t="n">
+        <v>522827123.1536865</v>
+      </c>
+      <c r="F36" t="n">
+        <v>672557644.7206413</v>
+      </c>
+      <c r="G36" t="n">
+        <v>431744544.6389621</v>
+      </c>
+      <c r="H36" t="n">
+        <v>246964439.8150785</v>
+      </c>
+      <c r="I36" t="n">
+        <v>672557644.7206413</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2007/af2057f32254ca19/provenance.json</t>
+        </is>
+      </c>
+      <c r="M36" t="n">
+        <v>5</v>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>2008</v>
+      </c>
+      <c r="B37" t="n">
+        <v>436038017.7851786</v>
+      </c>
+      <c r="C37" t="n">
+        <v>298850808.0082095</v>
+      </c>
+      <c r="D37" t="n">
+        <v>255480744.7193927</v>
+      </c>
+      <c r="E37" t="n">
+        <v>525234501.729224</v>
+      </c>
+      <c r="F37" t="n">
+        <v>707933361.0216</v>
+      </c>
+      <c r="G37" t="n">
+        <v>436038017.7851786</v>
+      </c>
+      <c r="H37" t="n">
+        <v>255480744.7193927</v>
+      </c>
+      <c r="I37" t="n">
+        <v>707933361.0216</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2008/51e4a448b1f4148f/provenance.json</t>
+        </is>
+      </c>
+      <c r="M37" t="n">
+        <v>5</v>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>2009</v>
+      </c>
+      <c r="B38" t="n">
+        <v>533166117.2568145</v>
+      </c>
+      <c r="C38" t="n">
+        <v>373782846.7119687</v>
+      </c>
+      <c r="D38" t="n">
+        <v>324922611.4735078</v>
+      </c>
+      <c r="E38" t="n">
+        <v>606602120.6501775</v>
+      </c>
+      <c r="F38" t="n">
+        <v>818089364.2668625</v>
+      </c>
+      <c r="G38" t="n">
+        <v>533166117.2568145</v>
+      </c>
+      <c r="H38" t="n">
+        <v>324922611.4735078</v>
+      </c>
+      <c r="I38" t="n">
+        <v>818089364.2668625</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2009/d16425bc4ac9cb7d/provenance.json</t>
+        </is>
+      </c>
+      <c r="M38" t="n">
+        <v>5</v>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>2010</v>
+      </c>
+      <c r="B39" t="n">
+        <v>560017900.3038681</v>
+      </c>
+      <c r="C39" t="n">
+        <v>414772163.8780107</v>
+      </c>
+      <c r="D39" t="n">
+        <v>354963696.8824489</v>
+      </c>
+      <c r="E39" t="n">
+        <v>616677563.6935568</v>
+      </c>
+      <c r="F39" t="n">
+        <v>853639153.3212062</v>
+      </c>
+      <c r="G39" t="n">
+        <v>560017900.3038681</v>
+      </c>
+      <c r="H39" t="n">
+        <v>354963696.8824489</v>
+      </c>
+      <c r="I39" t="n">
+        <v>853639153.3212062</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2010/5d2cc2c9685a81c9/provenance.json</t>
+        </is>
+      </c>
+      <c r="M39" t="n">
+        <v>5</v>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B40" t="n">
+        <v>534489179.709148</v>
+      </c>
+      <c r="C40" t="n">
+        <v>390866290.8003881</v>
+      </c>
+      <c r="D40" t="n">
+        <v>336878132.354686</v>
+      </c>
+      <c r="E40" t="n">
+        <v>563050768.2837955</v>
+      </c>
+      <c r="F40" t="n">
+        <v>855112051.2819391</v>
+      </c>
+      <c r="G40" t="n">
+        <v>534489179.709148</v>
+      </c>
+      <c r="H40" t="n">
+        <v>336878132.354686</v>
+      </c>
+      <c r="I40" t="n">
+        <v>855112051.2819391</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2011/a6c24b780ceeb354/provenance.json</t>
+        </is>
+      </c>
+      <c r="M40" t="n">
+        <v>5</v>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B41" t="n">
+        <v>522018895.4048831</v>
+      </c>
+      <c r="C41" t="n">
+        <v>372486618.4135149</v>
+      </c>
+      <c r="D41" t="n">
+        <v>330496500.0746879</v>
+      </c>
+      <c r="E41" t="n">
+        <v>552965034.7905351</v>
+      </c>
+      <c r="F41" t="n">
+        <v>847857525.0531121</v>
+      </c>
+      <c r="G41" t="n">
+        <v>522018895.4048831</v>
+      </c>
+      <c r="H41" t="n">
+        <v>330496500.0746879</v>
+      </c>
+      <c r="I41" t="n">
+        <v>847857525.0531121</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2012/2fd3c52e363d2259/provenance.json</t>
+        </is>
+      </c>
+      <c r="M41" t="n">
+        <v>5</v>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B42" t="n">
+        <v>482254674.1004324</v>
+      </c>
+      <c r="C42" t="n">
+        <v>358163665.9225335</v>
+      </c>
+      <c r="D42" t="n">
+        <v>308464456.7167505</v>
+      </c>
+      <c r="E42" t="n">
+        <v>527865943.3543385</v>
+      </c>
+      <c r="F42" t="n">
+        <v>786760558.9213361</v>
+      </c>
+      <c r="G42" t="n">
+        <v>482254674.1004324</v>
+      </c>
+      <c r="H42" t="n">
+        <v>308464456.7167505</v>
+      </c>
+      <c r="I42" t="n">
+        <v>786760558.9213361</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2013/821becabd572bab5/provenance.json</t>
+        </is>
+      </c>
+      <c r="M42" t="n">
+        <v>5</v>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B43" t="n">
+        <v>461511239.7453014</v>
+      </c>
+      <c r="C43" t="n">
+        <v>332535908.5751317</v>
+      </c>
+      <c r="D43" t="n">
+        <v>285532500.7216681</v>
+      </c>
+      <c r="E43" t="n">
+        <v>475722477.7854884</v>
+      </c>
+      <c r="F43" t="n">
+        <v>768724200.6075588</v>
+      </c>
+      <c r="G43" t="n">
+        <v>461511239.7453014</v>
+      </c>
+      <c r="H43" t="n">
+        <v>285532500.7216681</v>
+      </c>
+      <c r="I43" t="n">
+        <v>768724200.6075588</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2014/c9d1725dde41256d/provenance.json</t>
+        </is>
+      </c>
+      <c r="M43" t="n">
+        <v>5</v>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B44" t="n">
+        <v>484498139.063188</v>
+      </c>
+      <c r="C44" t="n">
+        <v>345579538.81687</v>
+      </c>
+      <c r="D44" t="n">
+        <v>302232237.8346015</v>
+      </c>
+      <c r="E44" t="n">
+        <v>458241357.1778029</v>
+      </c>
+      <c r="F44" t="n">
+        <v>746814849.4849148</v>
+      </c>
+      <c r="G44" t="n">
+        <v>458241357.1778029</v>
+      </c>
+      <c r="H44" t="n">
+        <v>302232237.8346015</v>
+      </c>
+      <c r="I44" t="n">
+        <v>746814849.4849148</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2015/9d39afaaa8b014f8/provenance.json</t>
+        </is>
+      </c>
+      <c r="M44" t="n">
+        <v>5</v>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B45" t="n">
+        <v>496230139.3074661</v>
+      </c>
+      <c r="C45" t="n">
+        <v>356617805.3361853</v>
+      </c>
+      <c r="D45" t="n">
+        <v>325455668.3389037</v>
+      </c>
+      <c r="E45" t="n">
+        <v>476980282.1449742</v>
+      </c>
+      <c r="F45" t="n">
+        <v>757825896.9804784</v>
+      </c>
+      <c r="G45" t="n">
+        <v>476980282.1449742</v>
+      </c>
+      <c r="H45" t="n">
+        <v>325455668.3389037</v>
+      </c>
+      <c r="I45" t="n">
+        <v>757825896.9804784</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2016/cfbe2d742214e408/provenance.json</t>
+        </is>
+      </c>
+      <c r="M45" t="n">
+        <v>5</v>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B46" t="n">
+        <v>438372514.8503831</v>
+      </c>
+      <c r="C46" t="n">
+        <v>347636211.3720878</v>
+      </c>
+      <c r="D46" t="n">
+        <v>288486362.8628082</v>
+      </c>
+      <c r="E46" t="n">
+        <v>497116817.0641422</v>
+      </c>
+      <c r="F46" t="n">
+        <v>722943149.2865001</v>
+      </c>
+      <c r="G46" t="n">
+        <v>438372514.8503831</v>
+      </c>
+      <c r="H46" t="n">
+        <v>288486362.8628082</v>
+      </c>
+      <c r="I46" t="n">
+        <v>722943149.2865001</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2017/e85bc3c6652e1ebf/provenance.json</t>
+        </is>
+      </c>
+      <c r="M46" t="n">
+        <v>5</v>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B47" t="n">
+        <v>424783299.3608181</v>
+      </c>
+      <c r="C47" t="n">
+        <v>335538007.8334042</v>
+      </c>
+      <c r="D47" t="n">
+        <v>279026034.8176643</v>
+      </c>
+      <c r="E47" t="n">
+        <v>512334031.7864357</v>
+      </c>
+      <c r="F47" t="n">
+        <v>727868609.4166429</v>
+      </c>
+      <c r="G47" t="n">
+        <v>424783299.3608181</v>
+      </c>
+      <c r="H47" t="n">
+        <v>279026034.8176643</v>
+      </c>
+      <c r="I47" t="n">
+        <v>727868609.4166429</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2018/786b5184701484b9/provenance.json</t>
+        </is>
+      </c>
+      <c r="M47" t="n">
+        <v>5</v>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B48" t="n">
+        <v>487323889.6140407</v>
+      </c>
+      <c r="C48" t="n">
+        <v>384683676.4787875</v>
+      </c>
+      <c r="D48" t="n">
+        <v>328160900.4953107</v>
+      </c>
+      <c r="E48" t="n">
+        <v>661472496.828328</v>
+      </c>
+      <c r="F48" t="n">
+        <v>834175483.6310664</v>
+      </c>
+      <c r="G48" t="n">
+        <v>487323889.6140407</v>
+      </c>
+      <c r="H48" t="n">
+        <v>328160900.4953107</v>
+      </c>
+      <c r="I48" t="n">
+        <v>834175483.6310664</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2019/e82a6f61f15e47c4/provenance.json</t>
+        </is>
+      </c>
+      <c r="M48" t="n">
+        <v>5</v>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:O48"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4460,136 +6133,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>Specific PPR for HS_048</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Simple method, applied per taxon: SPPR = (1/TE)^(TL-1), TE = 0.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>taxon</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>trophic_level</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>sppr_simple</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Cephalopoda</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>3.81</v>
-      </c>
-      <c r="C5" t="n">
-        <v>645.654229</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Chionobathyscus dewitti</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="C6" t="n">
-        <v>575.439937</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Rajiformes</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>3.61</v>
-      </c>
-      <c r="C7" t="n">
-        <v>407.380278</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Trematomus eulepidotus</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="C8" t="n">
-        <v>223.872114</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Marine fishes not identified</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="C9" t="n">
-        <v>190.546072</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Cnidaria</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="C10" t="n">
-        <v>31.622777</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>No Ecopath model has been extracted for this ecosystem yet,</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>so the network-based SPPR methods are not available here.</t>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>No final mappings are available for this ecosystem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Models without a recorded mapping are not assigned invented taxon groups or weights.</t>
         </is>
       </c>
     </row>
@@ -4604,43 +6164,136 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>Group SPPR: all</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>All basal sources, including imports. Models are separate. Blank means unavailable, not zero.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>model</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>group_name</t>
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Specific PPR for HS_048</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Simple method, applied per taxon: SPPR = (1/TE)^(TL-1), TE = 0.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>taxon</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>trophic_level</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>sppr_simple</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>No extracted model is available for this ecosystem.</t>
+          <t>Cephalopoda</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="C5" t="n">
+        <v>645.654229</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Chionobathyscus dewitti</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="C6" t="n">
+        <v>575.439937</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Rajiformes</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="C7" t="n">
+        <v>407.380278</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Trematomus eulepidotus</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="C8" t="n">
+        <v>223.872114</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Marine fishes not identified</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="C9" t="n">
+        <v>190.546072</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Cnidaria</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C10" t="n">
+        <v>31.622777</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>No Ecopath model has been extracted for this ecosystem yet,</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>so the network-based SPPR methods are not available here.</t>
         </is>
       </c>
     </row>
@@ -4665,14 +6318,14 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Group SPPR: inner</t>
+          <t>Group SPPR: all</t>
         </is>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Internal sources: primary producers and detritus; excludes imports. Models are separate. Blank means unavailable, not zero.</t>
+          <t>All basal sources, including imports. Models are separate. Blank means unavailable, not zero.</t>
         </is>
       </c>
     </row>
@@ -4716,14 +6369,14 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Group SPPR: PP</t>
+          <t>Group SPPR: inner</t>
         </is>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Primary producers only; excludes detritus and imports. Models are separate. Blank means unavailable, not zero.</t>
+          <t>Internal sources: primary producers and detritus; excludes imports. Models are separate. Blank means unavailable, not zero.</t>
         </is>
       </c>
     </row>
@@ -4752,6 +6405,57 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Group SPPR: PP</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Primary producers only; excludes detritus and imports. Models are separate. Blank means unavailable, not zero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>group_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>No extracted model is available for this ecosystem.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4837,7 +6541,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5975,132 +7679,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>Net primary production, 2019, tonnes carbon per year</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>satellite_model</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>npp_tC_yr</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Antoine-Morel</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>414048303.1417124</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>VGPM</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>326841402.3751328</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Eppley</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>278817572.6725649</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>CbPM</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>562011366.0005356</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>CAFE</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>708746176.5796206</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>ensemble median</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>414048303.1417124</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>ensemble min</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>278817572.6725649</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>ensemble max</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>708746176.5796206</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>water area (km2)</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>8775554.954823056</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>